--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 63 of 77 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file was kept up to date through ADR-077 (this sprint).</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 64 of 78 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-078.</t>
         </is>
       </c>
     </row>
@@ -165,7 +165,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No. 7 ADRs are formally superseded (whole or in part), 3 are only partly built, 2 are not built, 2 are deferred by the owner. Four headers (ADR-019, 032, 033, 037) still read plain 'Accepted' although a later ADR or event changed their meaning (see 'Stale headers').</t>
+          <t xml:space="preserve">No. 7 ADRs are formally superseded (whole or in part), 3 are only partly built, 2 are not built, 2 are deferred by the owner. Four headers (ADR-019, 032, 033, 037) that once read plain 'Accepted' although a later ADR or event had changed their meaning now say so (Sprint 67); 'Stale headers' lists the decisions whose header says nothing of how far they are built.</t>
         </is>
       </c>
     </row>
@@ -177,7 +177,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No. A rewrite would lose the reasoning and the trade-offs, which are the point of an ADR. Recommended: a one-line status edit on four headers, and keep this register as the shareable index.</t>
+          <t xml:space="preserve">No. A rewrite would lose the reasoning and the trade-offs, which are the point of an ADR. Keep this register as the shareable index, and regenerate it with scripts/build_adr_register.py when an ADR is added.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at the Sprint 66 commit (c7c7d7c).</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit f4e0313 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted</t>
+          <t xml:space="preserve">Accepted. Superseded in part by ADR-040 (the tooling: structured JSON logs to stdout). OpenTelemetry, Prometheus and Grafana remain the destination and are deferred, not built.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ADR-040</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted (September 2026)</t>
+          <t xml:space="preserve">Accepted (September 2026). Superseded in part by ADR-038 (the organisation half: email one-time code, no password). The rule that a candidate signs up by phone still governs.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ADR-038</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted (September 2026)</t>
+          <t xml:space="preserve">Accepted (September 2026). Superseded in part by ADR-041 (the two-language assumption: a language is a messages file and rows). Hindi and English remain the launch pair.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ADR-041</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted (September 2026)</t>
+          <t xml:space="preserve">Accepted (September 2026). Superseded in part by ADR-038 (the authenticated employer console ships to production, behind a sign-in). The rule that no employer-facing payload identifies a candidate stands and is tested; only the unauthenticated demonstration console is local-only.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ADR-038</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5967,8 +5967,80 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Phone Holds No Data the Website Does Not, Edits a History Section Through One Table Checked Against the Schema, and Keeps a Course Budget Only on the Device and Only Until Sign-Out</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- A phone adds no data type the website does not hold. The Data Safety and App Privacy answers (docs/release/privacy-and-data-safety.md) are unchanged. Date of birth and gender stay web-only: they are optional and sensitive, nothing on the phone needs them, and a phone is the device most likely to be shared. A person's salary range, notice period, work type, willingness to move and alert opt-out are the same…</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 67 (BL-15.9 to BL-15.11, M6 of the mobile programme). Extends ADR-048, ADR-049, ADR-068, ADR-072 and ADR-074. No migration, no new endpoint: five operations that the website already calls join the released surface (46 to 51, additive only).</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-048, ADR-049, ADR-068, ADR-072, ADR-074</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 67 (M6). Candidate parity on the phone: history sections, why-not-me, careers, budget. Tested and browser-run; not run on a device.</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N78"/>
+  <autoFilter ref="A1:N79"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -6015,7 +6087,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADR-019 Observability Strategy</t>
+          <t xml:space="preserve">ADR-005 AI Strategy</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -6025,105 +6097,105 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tooling half replaced by ADR-040 (structured JSON logs to stdout). The destination (OpenTelemetry, Prometheus, Grafana) remains deferred and unbuilt.</t>
+          <t xml:space="preserve">No LLM call exists anywhere; the intelligence/ module has an ADR and no code. The direction stands: ADR-036 keeps every decision deterministic and lets a model only explain.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Header silent about a later ADR or event</t>
+          <t xml:space="preserve">Decision stands; header says nothing of implementation lag</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Superseded in part by ADR-040 (tooling); destination deferred.</t>
+          <t xml:space="preserve">Accepted; not built.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADR-032 Primary Credential by Actor Type</t>
+          <t xml:space="preserve">ADR-011 Identity Model</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted (September 2026)</t>
+          <t xml:space="preserve">Accepted</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The organisation half (email OTP, password-free) is replaced by ADR-038; the credential-follows-actor rule still governs sign-up.</t>
+          <t xml:space="preserve">UUID primary key built. Optional Aadhaar verification is not built and nothing collects Aadhaar data.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Header silent about a later ADR or event</t>
+          <t xml:space="preserve">Decision stands; header says nothing of implementation lag</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Superseded in part by ADR-038 (organisation half).</t>
+          <t xml:space="preserve">Accepted; Aadhaar verification not built.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADR-033 Language Scope at Launch</t>
+          <t xml:space="preserve">ADR-013 Embedding Strategy</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted (September 2026)</t>
+          <t xml:space="preserve">Accepted</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The two-language assumption is replaced by ADR-041 (a language is a messages file and rows). Hindi and English remain the launch pair; Malay is hidden from the switcher, not removed.</t>
+          <t xml:space="preserve">pgvector storage and a 384-dimension port are built (ADR-031). The mandated sentence-transformers model is not switched on: HashingEmbeddingProvider is an honest placeholder and BL-5.3 is not started.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Header silent about a later ADR or event</t>
+          <t xml:space="preserve">Decision stands; header says nothing of implementation lag</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Superseded in part by ADR-041 (two-language assumption).</t>
+          <t xml:space="preserve">Accepted; placeholder embedder in use (BL-5.3).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADR-037 The Employer Console as a Labelled Demonstration</t>
+          <t xml:space="preserve">ADR-018 AI Model Strategy</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted (September 2026)</t>
+          <t xml:space="preserve">Accepted</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The rule that no employer-facing payload identifies a candidate stands and is tested. The 'unauthenticated demonstration' framing no longer describes the product: the authenticated employer console shipped to production in Sprint 12 (ADR-038); only the unauthenticated demo console is local-only.</t>
+          <t xml:space="preserve">No external LLM is integrated. The adapter pattern it depends on exists (ADR-017, ADR-031).</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Header silent about a later ADR or event</t>
+          <t xml:space="preserve">Decision stands; header says nothing of implementation lag</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Superseded in part: console is authenticated and ships to production (ADR-038); de-identification rule stands.</t>
+          <t xml:space="preserve">Accepted; not built.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADR-005 AI Strategy</t>
+          <t xml:space="preserve">ADR-023 Data Privacy &amp; Compliance</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -6133,7 +6205,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No LLM call exists anywhere; the intelligence/ module has an ADR and no code. The direction stands: ADR-036 keeps every decision deterministic and lets a model only explain.</t>
+          <t xml:space="preserve">Consent record, DPDP export, erasure, the redaction filter and retention are built. The encryption path for Aadhaar, resumes and assessment results is not, so that data is deliberately not collected.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -6143,24 +6215,24 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted; not built.</t>
+          <t xml:space="preserve">Accepted; encryption path unbuilt.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADR-011 Identity Model</t>
+          <t xml:space="preserve">ADR-025 Monetization Model</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted</t>
+          <t xml:space="preserve">Accepted (September 2026)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UUID primary key built. Optional Aadhaar verification is not built and nothing collects Aadhaar data.</t>
+          <t xml:space="preserve">Monetisation (BL-1.3) is a standing not-started: the owner chose to wait for real traffic. ADR-043 and ADR-047 carry the deferral.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -6170,24 +6242,24 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted; Aadhaar verification not built.</t>
+          <t xml:space="preserve">Accepted; deferred by owner.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADR-013 Embedding Strategy</t>
+          <t xml:space="preserve">ADR-028 Cloud Platform and Deployment Topology</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted</t>
+          <t xml:space="preserve">Accepted (September 2026)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pgvector storage and a 384-dimension port are built (ADR-031). The mandated sentence-transformers model is not switched on: HashingEmbeddingProvider is an honest placeholder and BL-5.3 is not started.</t>
+          <t xml:space="preserve">Nothing is deployed anywhere; deployment is deferred by the owner and is now on the mobile launch's critical path. Still the intended topology.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -6197,120 +6269,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted; placeholder embedder in use (BL-5.3).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADR-018 AI Model Strategy</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accepted</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No external LLM is integrated. The adapter pattern it depends on exists (ADR-017, ADR-031).</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decision stands; header says nothing of implementation lag</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accepted; not built.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADR-023 Data Privacy &amp; Compliance</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accepted</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consent record, DPDP export, erasure, the redaction filter and retention are built. The encryption path for Aadhaar, resumes and assessment results is not, so that data is deliberately not collected.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decision stands; header says nothing of implementation lag</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accepted; encryption path unbuilt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADR-025 Monetization Model</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accepted (September 2026)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monetisation (BL-1.3) is a standing not-started: the owner chose to wait for real traffic. ADR-043 and ADR-047 carry the deferral.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decision stands; header says nothing of implementation lag</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accepted; deferred by owner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADR-028 Cloud Platform and Deployment Topology</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accepted (September 2026)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nothing is deployed anywhere; deployment is deferred by the owner and is now on the mobile launch's critical path. Still the intended topology.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decision stands; header says nothing of implementation lag</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">Accepted; deferred by owner, nothing deployed.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -6810,8 +6774,30 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 67</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-078</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Phone Holds No Data the Website Does Not, Edits a History Section Through One Table Checked Against the Schema, and Keeps a Course Budget Only on the Device and Only Until Sign-Out</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D22"/>
+  <autoFilter ref="A1:D23"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit f4e0313 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 4477bef by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 64 of 78 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-078.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 65 of 79 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-079.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 4477bef by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 6411ef6 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
     </row>
@@ -6039,8 +6039,80 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Listing Says What Decides Whether to Open It in the Units People Use, a Rule Both Clients Share Is Tested Against One File, a Count Comes From the Server, and Touch and Type Have Floors a Browser Test Holds</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- A card carries what decides whether to open it, in the order people ask: what, who, where, how much, by when. The employer carries a verified mark when it has earned one; a card never says "not verified", because in a list the absence of a mark would read as an accusation of every employer without one, and the vacancy's own page is where "not yet verified" and "never pay to apply" are stated. The NSQF level and…</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 69 (BL-16.1, from the UI review of Sprint 68). Extends ADR-037, ADR-065, ADR-068, ADR-072 and ADR-074. No migration. One endpoint is new (GET /jobs/states, public, additive) and the two operator queues change shape (/ops/organisations and /ops/candidates/certifications return {items, total, limit, offset}); neither is in the released mobile surface, which stays at 51.</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-037, ADR-065, ADR-068, ADR-072, ADR-074</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 69 (BL-16.1). Scannable listings: monthly pay, card v2, server totals, a shared fixture for rules both clients need, 12 px and 44 px floors held by tests.</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N79"/>
+  <autoFilter ref="A1:N80"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -6796,8 +6868,30 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 69</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-079</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Listing Says What Decides Whether to Open It in the Units People Use, a Rule Both Clients Share Is Tested Against One File, a Count Comes From the Server, and Touch and Type Have Floors a Browser Test Holds</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D23"/>
+  <autoFilter ref="A1:D24"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 65 of 79 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-079.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 66 of 80 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-080.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 6411ef6 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 021c147 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
     </row>
@@ -6111,8 +6111,80 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Match Is Explained in a Sentence Built From the Fields the Scorer Returned, a Count of Matches Comes From Where the Rows Are, and the First Screen Is the Person's Own</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- A match is said in a sentence, from the lists the scorer returned and nothing else. matchSummary(matched, missing) (web lib/match-summary.ts, phone core/match-summary.ts, both run over tests/fixtures/match_summary_cases.json, ADR-079's pattern, a Python test holds that both read it) counts the two lists after the vacancy page's presentation rules (presentRequirements): one standard listed under two codes counts…</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 70 (BL-16.2, from the UI review of Sprint 68). Extends ADR-036, ADR-037, ADR-074 and ADR-079. No migration, no new operation: one existing field (total on GET /me/matches) now says what it always claimed, and the released surface stays at 51.</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-036, ADR-037, ADR-074, ADR-079</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 70 (BL-16.2). A match said in a sentence from the scorer's fields, a true match total, a task-first homepage and a signed-in phone home. Expert judgement, not user research.</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N80"/>
+  <autoFilter ref="A1:N81"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -6890,8 +6962,30 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 70</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-080</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Match Is Explained in a Sentence Built From the Fields the Scorer Returned, a Count of Matches Comes From Where the Rows Are, and the First Screen Is the Person's Own</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D24"/>
+  <autoFilter ref="A1:D25"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 66 of 80 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-080.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 67 of 81 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-081.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 021c147 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit c373a5d by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
     </row>
@@ -6183,8 +6183,80 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role-Search Vocabulary Is Measured Against Titles Written Before It, a Hold-Out Is Reported Separately, and an Unreviewed Draft Says So Where a Reviewer Will Find It</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Titles are written before the aliases and not from what search answers. tests/fixtures/role_titles.json holds 146 titles people say (118 English, 12 romanised Hindi, 16 Devanagari) across the sectors. Each carries the corpus roles that honestly fit, chosen by meaning from a listing of the corpus (an exact name, or a case-insensitive pattern over role names), or none_ok for a job the corpus has no role for, with…</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 71 (BL-12.12). Extends ADR-050 and ADR-054. No migration, no new operation (the released surface stays at 51), and no ranking change.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-050, ADR-054</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 71 (BL-12.12). Role-alias coverage 41 to 88 roles, measured against titles written first; the hold-out did not move (37.5%) and is reported. Unreviewed draft, flagged.</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N81"/>
+  <autoFilter ref="A1:N82"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -6984,8 +7056,30 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 71</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-081</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role-Search Vocabulary Is Measured Against Titles Written Before It, a Hold-Out Is Reported Separately, and an Unreviewed Draft Says So Where a Reviewer Will Find It</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D25"/>
+  <autoFilter ref="A1:D26"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 67 of 81 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-081.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 68 of 82 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-082.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit c373a5d by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit b459fa7 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">68</t>
         </is>
       </c>
     </row>
@@ -6255,8 +6255,80 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Withdrawing Consent Is a Pause the Account Survives, a Changed Notice Is Confirmed and Never Enforced, and the Notice Is Checked Against the Data</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0056</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Withdrawing consent pauses the account and keeps it (users.consent_withdrawn_at). Its effects are each read at one choke point and each has a test that fails without it: the person is out of every employer pool, alert sweep and public people figure (marketplace.paused_profile(), used by matching.retrieval.candidate_pair_facts and skilled_profile()); applying and registering interest refuse with 409…</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 72 (the DPDP readiness slice). Extends ADR-023, ADR-055, ADR-069 and ADR-071. Migration 0056 (one column and a partial index). Three operations (GET/POST /me/account/consent, POST /me/account/consent/withdraw) and two derived fields on UserOut (consent_current, consent_withdrawn), all additive: the released surface goes from 51 to 54 operations, the old 51 untouched.</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-023, ADR-055, ADR-069, ADR-071</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 72. Consent withdrawn without deleting (a pause), re-consent that never blocks, an 18+ rule, a notice checked against the data, an incident runbook. Pause is not erasure: a question for counsel.</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N82"/>
+  <autoFilter ref="A1:N83"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -7078,8 +7150,30 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 72</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-082</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Withdrawing Consent Is a Pause the Account Survives, a Changed Notice Is Confirmed and Never Enforced, and the Notice Is Checked Against the Data</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0056</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D26"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 68 of 82 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-082.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 69 of 83 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-083.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit b459fa7 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit f07728c by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
     </row>
@@ -6327,8 +6327,80 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Hiring Side Gets One Primary Action Per Row and a Back Office You Can Jump Around, a Reference Panel Is Folded and Loaded When Opened, and a Finding Is Read Against the Code Before It Is Fixed</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- /admin: the daily work first and open, the reference panels folded, one nav. Overview, Verification, Grievances and Reports stay on the page; Programme outcomes, the district skill gap, Role aliases and Enrolment are closed &lt;details&gt; rows of fixed height (CollapsiblePanel), and AdminNav is a sticky row of eight native anchors (44 px, scrolling sideways on a phone, wrapping from sm up, Enrolment shown to the…</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 73 (UI-14, UI-15, UI-16 and UI-26 of the Sprint 68 review). Extends ADR-065 (no layout shift), ADR-079 (a 44 px floor) and ADR-082. No migration, no new operation; the released surface stays at 54.</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-065, ADR-079, ADR-082</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 73 (UI-14, 15, 16, 26). A jump nav and folded, lazily loaded panels on /admin, one primary action per row, an overview that keeps its shape. UI-26 was mis-stated: it was the seed. Expert judgement, not user research.</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N83"/>
+  <autoFilter ref="A1:N84"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -7172,8 +7244,30 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 73</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-083</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Hiring Side Gets One Primary Action Per Row and a Back Office You Can Jump Around, a Reference Panel Is Folded and Loaded When Opened, and a Finding Is Read Against the Code Before It Is Fixed</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D28"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 69 of 83 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-083.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 70 of 84 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-084.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit f07728c by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 5d069db by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">70</t>
         </is>
       </c>
     </row>
@@ -6399,8 +6399,80 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Vacancy's Posted Date Is Stamped at Every Writer of "Published" and Never Invented, a Role You Confirm Is Saved Only by Your Own Act, and a Story Whose Data Does Not Exist Is Deferred With the Finding</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0057</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- jobs.published_at, nullable, not backfilled. Every vacancy published before the column existed keeps NULL and the clients say nothing for NULL. A backfill from created_at would show a draft's date as a posting date. - One function keeps it true to status, and every writer of "published" calls it (takedown.stamp_publication, beside refuse_while_taken_down, the ADR-069 convention). Going live from not-live stamps…</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 74 (the first story of "candidate depth": the posted date Sprint 69 could not show, and BL-6.5). Extends ADR-049 (career ladders store nothing; this stores one fact, by the person's act), ADR-069 (list every writer of "published"), ADR-079 (a rule two clients need is written twice and run over one file) and ADR-082 (a new column on a person is in the notice, the export and the erasure). Migration 0057, additive response and request fields only; the released surface stays at 54 operations.</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-049, ADR-069, ADR-079, ADR-082</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N84"/>
+  <autoFilter ref="A1:N85"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -7266,8 +7338,30 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 74</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-084</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Vacancy's Posted Date Is Stamped at Every Writer of "Published" and Never Invented, a Role You Confirm Is Saved Only by Your Own Act, and a Story Whose Data Does Not Exist Is Deferred With the Finding</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0057</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D28"/>
+  <autoFilter ref="A1:D29"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 70 of 84 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-084.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 71 of 85 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-085.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 5d069db by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit b7d69ab by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">71</t>
         </is>
       </c>
     </row>
@@ -6471,8 +6471,80 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Course Counts Toward a Qualification Because Its Provider Says So, and a Learner Is Told Whose Word It Is; a List Is Ordered by Something Unique</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- The provider links a course; the link is checked before anything changes. CourseIn.qualification_pack_code (blank is none) is written by create_course and update_course, and listings.require_current_pack answers 422 in words for a code that names no current pack, before the first field is set (the Sprint 55 rule; a mutation that moved it after the loop was caught only once a test called the service and then…</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 75 (BL-12.8, unblocked; and the newest-first sort Sprint 74's posted date made possible). Extends ADR-084 (a date read from a column that is NULL when nobody knows), ADR-064 (a bulk upload changes only the columns the file carries), ADR-080 (the seeker's first screens avoid the framework's vocabulary) and ADR-047 (a status the platform cannot verify is the provider's, and is labelled so). No migration, additive API only; the released surface stays at 54 operations.</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-047, ADR-064, ADR-080, ADR-084</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N85"/>
+  <autoFilter ref="A1:N86"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -7360,8 +7432,30 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 75</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-085</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Course Counts Toward a Qualification Because Its Provider Says So, and a Learner Is Told Whose Word It Is; a List Is Ordered by Something Unique</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D29"/>
+  <autoFilter ref="A1:D30"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 71 of 85 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-085.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 72 of 86 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-086.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit b7d69ab by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 3b57ff6 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71</t>
+          <t xml:space="preserve">72</t>
         </is>
       </c>
     </row>
@@ -6543,8 +6543,80 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Look Is Chosen in One Place: Colour Ramps, a Named Type Scale and Shape Tokens in `globals.css`, Generated Into the Phone; a Ramp Step Is Never a Class, and Text Is Never Translucent</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Two ramps, defined once. --brand-50 to --brand-900 (700 is today's #1f4e79; the dark theme's primary is 400) and --neutral-50 to --neutral-950 (tinted to the brand hue), as variables in globals.css. The semantic tokens (background, surface, border, control edge, muted text, brand, the four tones) are re-pointed at steps in both themes. The page is neutral-50 and a card is white, so a card is a surface instead…</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 77 (Epic B19, BL-19.4, BL-19.5, BL-19.6). Extends ADR-065 (a page must not jump while it loads; the Hindi fold is a budget), ADR-077 (accessibility is held by the props that produce it) and ADR-079 (floors are asserted where they hold for every page); implements the direction the Product Owner signed off in docs/design/design-brief.md (Sprint 76). Frontend only: no migration, no API or contract change, the released surface stays at 54 operations.</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-065, ADR-077, ADR-079</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N86"/>
+  <autoFilter ref="A1:N87"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -7454,8 +7526,30 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 77</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-086</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Look Is Chosen in One Place: Colour Ramps, a Named Type Scale and Shape Tokens in `globals.css`, Generated Into the Phone; a Ramp Step Is Never a Class, and Text Is Never Translucent</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D30"/>
+  <autoFilter ref="A1:D31"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 72 of 86 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-086.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 73 of 87 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-087.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 3b57ff6 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 1fabbae by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72</t>
+          <t xml:space="preserve">73</t>
         </is>
       </c>
     </row>
@@ -6615,8 +6615,80 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Icons Are Drawn Once and Imported One at a Time, the Revamp Is Held by Ratchets That Only Go Down, and a Person May Choose Light or Dark Without the First Load Paying for It</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Thirty-four icons, drawn once, imported one at a time. web/src/components/ui/icons.tsx holds makeIcon("Name", [paths]) calls, each marked /#__PURE__/, on a 24 grid with a 2 px round stroke in currentColor: no package, no image request, no download. Each icon is its own export so a route pays only for the icons it imports; a table looked up by name would put every shape on every route. An icon beside its word is…</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 78 (Epic B19, BL-19.7 icon set, BL-19.9 guards for the revamp, BL-19.8 theme control). Extends ADR-086 (tokens), ADR-065 (a page must not jump while it loads), ADR-077 (accessibility is held by the props that produce it) and ADR-079 (floors are asserted where they hold for every page). Frontend only: no migration, no API or contract change, the released surface stays at 54 operations.</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-065, ADR-077, ADR-079, ADR-086</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N87"/>
+  <autoFilter ref="A1:N88"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -7548,8 +7620,30 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 78</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-087</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Icons Are Drawn Once and Imported One at a Time, the Revamp Is Held by Ratchets That Only Go Down, and a Person May Choose Light or Dark Without the First Load Paying for It</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D31"/>
+  <autoFilter ref="A1:D32"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 73 of 87 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-087.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 74 of 88 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-088.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 1fabbae by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit f32ae25 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73</t>
+          <t xml:space="preserve">74</t>
         </is>
       </c>
     </row>
@@ -6687,8 +6687,80 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Form Field Says What Is Wrong Next to Itself, in the Page's Words or the Server's; the Library's Controls Are the Old Helpers Under the Same Names, and What a Form Does Not Need at First Paint Is Fetched When It Is Opened</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- One library, components/ui/field.tsx, and the old names stay. Field (label, hint, problem), Input, Textarea, Select and Checkbox; components/profile/fields.tsx re-exports them as Field, Text, Area, Select, Check, so the 25 forms that use them changed none of their markup and the limits (minLength={3}) stay literal at each control where constraints.test.ts reads them. Field provides a context; the control reads…</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 79 (Epic B19, BL-19.10, first half: the library, the validation and the four forms that matter most; the other raw controls move in the page-family stories). Extends ADR-086 (tokens), ADR-087 (ratchets, the header graph and the first-load budget) and the Sprint 29 and 30 conventions that a form mirrors the server's limits and never throws away what the server said. Frontend only: no migration, no API or contract change (54 operations).</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-086, ADR-087</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N88"/>
+  <autoFilter ref="A1:N89"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -7642,8 +7714,30 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 79</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-088</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Form Field Says What Is Wrong Next to Itself, in the Page's Words or the Server's; the Library's Controls Are the Old Helpers Under the Same Names, and What a Form Does Not Need at First Paint Is Fetched When It Is Opened</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D32"/>
+  <autoFilter ref="A1:D33"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 74 of 88 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-088.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 75 of 89 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-089.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit f32ae25 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit b83d88e by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74</t>
+          <t xml:space="preserve">75</t>
         </is>
       </c>
     </row>
@@ -6759,8 +6759,80 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-089</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Card Has a Level, a Status Has a Shape, an Empty List Has an Icon and a Slot for Art, and a Gallery Shows Them All in a Build That Is Never Shipped</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- A card has a level. Card level="default | raised | inset | interactive": the default is what it always was plus the soft shadow (the page is grey and a card is white, ADR-086), raised is the floating surface (a menu, a dialog's panel), inset is a box inside a card (the muted surface, no shadow: a bordered, shadowed card in a card was how a form held a sub-panel), and interactive lifts on hover and takes the…</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 80 (Epic B19, BL-19.11 surfaces and actions, BL-19.12 empty, loading and status states). Extends ADR-086 (tokens), ADR-087 (the icon set, the header graph and the first-load budget) and ADR-088 (the form library). Frontend only: no migration, no API or contract change (54 operations).</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-086, ADR-087, ADR-088</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N89"/>
+  <autoFilter ref="A1:N90"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -7736,8 +7808,30 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 80</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-089</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Card Has a Level, a Status Has a Shape, an Empty List Has an Icon and a Slot for Art, and a Gallery Shows Them All in a Build That Is Never Shipped</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D33"/>
+  <autoFilter ref="A1:D34"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 75 of 89 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-089.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 76 of 90 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-090.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit b83d88e by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 395d925 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">76</t>
         </is>
       </c>
     </row>
@@ -6831,8 +6831,80 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-090</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Job Seeker's Pages Are One Tap Away, the Bottom Bar Is a Chunk Whose Room Is Made Before It Arrives, and the Header Says Where You Are</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- The page you are on is marked. currentHref (lib/nav.ts, pure) picks the longest link that is the path or a parent of it: /employer/acme/jobs/x/applications is the vacancies page's and /employer/acme/team is the team's, never both. The desktop and mobile nav links are aria-current="page" and drawn filled, so it is not told by colour alone. A link to a place in a page (/#how-it-works) can never be current,…</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 81 (Epic B19, BL-19.13). Extends ADR-065 (a page must not jump while it loads), ADR-086 and ADR-087 (tokens, the header graph and the first-load budget) and ADR-089 (the surfaces and the barrel). Frontend only: no migration, no API or contract change (54 operations).</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-065, ADR-086, ADR-087, ADR-089</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N90"/>
+  <autoFilter ref="A1:N91"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -7830,8 +7902,30 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 81</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-090</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Job Seeker's Pages Are One Tap Away, the Bottom Bar Is a Chunk Whose Room Is Made Before It Arrives, and the Header Says Where You Are</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D34"/>
+  <autoFilter ref="A1:D35"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 76 of 90 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-090.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 77 of 91 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-091.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 395d925 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 42801e9 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
+          <t xml:space="preserve">77</t>
         </is>
       </c>
     </row>
@@ -6903,8 +6903,80 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-091</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Phone Gets the Web's Vocabulary, a Bar With Icons, and a Me Tab That Reads as Places</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- One vocabulary on both clients. Button has primary, secondary, ghost, danger and soft, each one row of tokens (background, edge, words) in one table, not five branches. Notice has info, success, warning and danger, each drawn with its shape (info, check, triangle, cross) so a tone is never colour alone; only a danger notice is announced (accessibilityRole="alert"). Badge gains danger and info; Card gains…</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 82 (Epic B19, BL-19.14, BL-19.21, BL-19.22). Extends ADR-072 (the phone is a second client of the same API), ADR-077 (accessibility is held by the props that produce it) and ADR-087 and ADR-089 (the icons, the tones and the surface levels it mirrors). Phone only and frontend only: no migration, no API or contract change (54 operations).</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-072, ADR-077, ADR-087, ADR-089</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N91"/>
+  <autoFilter ref="A1:N92"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -7924,8 +7996,30 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 82</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-091</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Phone Gets the Web's Vocabulary, a Bar With Icons, and a Me Tab That Reads as Places</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D35"/>
+  <autoFilter ref="A1:D36"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 77 of 91 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-091.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 78 of 92 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-092.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 42801e9 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 8b2742f by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">78</t>
         </is>
       </c>
     </row>
@@ -6975,8 +6975,80 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-092</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Phone's Profile Is a Stack of Sections, and a Home That Arrives in Pieces Waits and Arrives Once</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- The profile is a progress header and four sections. The header is a progress bar (ProgressBar: a progressbar role with its value, clamped to 0 to 100, a number that is not one is drawn as 0) beside the sentence that says the same number. Then, in the order a person fills them in: My skills (the role picker and what is held), About you, Your history (the six sections as ListRows, each with its count in the…</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 83 (Epic B19, BL-19.23 and the second half of BL-19.22). Extends ADR-065 (a page must not jump while it loads), ADR-078 (the profile's forms are one table compared with the server) and ADR-091 (the phone's vocabulary). Phone only and frontend only: no migration, no API or contract change (54 operations).</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-065, ADR-078, ADR-091</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N92"/>
+  <autoFilter ref="A1:N93"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8018,8 +8090,30 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 83</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-092</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Phone's Profile Is a Stack of Sections, and a Home That Arrives in Pieces Waits and Arrives Once</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D36"/>
+  <autoFilter ref="A1:D37"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 78 of 92 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-092.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 79 of 93 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-093.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 8b2742f by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit f6c93bc by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78</t>
+          <t xml:space="preserve">79</t>
         </is>
       </c>
     </row>
@@ -7047,8 +7047,80 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-093</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One Card for a Vacancy and a Course, Filters as a Row of Native Chips, and a Score a Seeker Can See Where They Look</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- One card, two uses. components/cards/JobCard and the new components/cards/CourseCard are the same shape: a mark for the organisation and the title in one row, the money as a tinted chip with a rupee, the place and (for a course) the start as icon chips, and a muted line for the rest (experience and how long ago; mode, language, level, credits, hours). The mark (ui/avatar) is a first letter on a tint chosen by…</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 84 (Epic B19, the first half of BL-19.15). Extends ADR-079 (a card says what decides whether to open it, and never accuses), ADR-086 and ADR-089 (tokens and surfaces), ADR-065 (a page must not jump while it loads) and ADR-068 (a recommendation says whether you can act on it). Web only and frontend only: no migration, no API or contract change (54 operations), no new icon.</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-065, ADR-068, ADR-079, ADR-086, ADR-089</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N93"/>
+  <autoFilter ref="A1:N94"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8112,8 +8184,30 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 84</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-093</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One Card for a Vacancy and a Course, Filters as a Row of Native Chips, and a Score a Seeker Can See Where They Look</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D37"/>
+  <autoFilter ref="A1:D38"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 79 of 93 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-093.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 80 of 94 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-094.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit f6c93bc by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit ef70c45 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79</t>
+          <t xml:space="preserve">80</t>
         </is>
       </c>
     </row>
@@ -7119,8 +7119,80 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-094</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Listing's Facts Are a Labelled Grid With an Icon, Who Is Behind It Is an Icon and a Sentence, and a Standard Is a Card Like the Others</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Three small pieces, written once, server components. ui/icon-tile (IconTile: an icon on a tinted square, five tones, two sizes, hidden from assistive technology because a word sits beside it), ui/fact (Facts, Fact, FactValue: a description list of labelled values with a small icon on each label, only div groups of dt and dd inside it, a wide value takes the row) and ui/trust-strip (TrustStrip: a shield on a…</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 85 (Epic B19, the second half of BL-19.15). Extends ADR-093 (one card for a vacancy and a course), ADR-079 (a card says what decides whether to open it, and never accuses), ADR-087 (icons are separate pure exports; nothing in the header graph imports them) and ADR-089 (surfaces have a level). Web only and frontend only: no migration, no API or contract change (54 operations), no new icon and no new message string (every word on these pages was already there; the phone is untouched).</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-079, ADR-087, ADR-089, ADR-093</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N94"/>
+  <autoFilter ref="A1:N95"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8206,8 +8278,30 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 85</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-094</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Listing's Facts Are a Labelled Grid With an Icon, Who Is Behind It Is an Icon and a Sentence, and a Standard Is a Card Like the Others</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D38"/>
+  <autoFilter ref="A1:D39"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 80 of 94 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-094.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 81 of 95 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-095.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit ef70c45 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 9b5af52 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80</t>
+          <t xml:space="preserve">81</t>
         </is>
       </c>
     </row>
@@ -7191,8 +7191,80 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-095</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Form's Controls Are the Library's and 44 px, a Row's Buttons Are Named for Their Row, and a Confirmation Keeps What the Person Typed</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Sign-in's two fields are the library's (Field + Input): a label tied to its control, a problem shown beside the field when it is left empty (aria-invalid, aria-describedby), 44 px (50 on the page's larger type). The code field keeps its look (centred, large, spaced) and its rules (digits only, six characters). "Use a different one", "Send a new code" and the "Create an account" link are 44 px; sign-up's code…</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 86 (Epic B19, BL-19.16). Extends ADR-088 (a field says what is wrong next to itself), ADR-079 (floors are asserted where they hold) and ADR-083 (every control at 44 px, one primary action per row). Web only and frontend only: no migration, no API or contract change (54 operations), no new icon (the apply confirmation uses the shield already in the set), no new message string.</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-079, ADR-083, ADR-088</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N95"/>
+  <autoFilter ref="A1:N96"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8300,8 +8372,30 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 86</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-095</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Form's Controls Are the Library's and 44 px, a Row's Buttons Are Named for Their Row, and a Confirmation Keeps What the Person Typed</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D39"/>
+  <autoFilter ref="A1:D40"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 81 of 95 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-095.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 82 of 96 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-096.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 9b5af52 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 6079039 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81</t>
+          <t xml:space="preserve">82</t>
         </is>
       </c>
     </row>
@@ -7263,8 +7263,80 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-096</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A State Is a Word With a Shape on a Card That Looks Like the Others, a Notice Has a Picture of Its Kind, and a Shared Section Takes Its Mark From the Page That Wants It</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- A state is StatusChip (ui/status-chip): the word, an icon and a tone from one table per list (APPLICATION_LOOK, INTEREST_LOOK), each a Record over the generated status type so a new state the server can say is a compile error here, not a chip with no shape. Nothing rests on colour (WCAG 1.4.1): "Shortlisted" and "Not selected" differ in word, shape and tone. A rejection is neutral, not red: it is the employer's…</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 87 (Epic B19, BL-19.17). Extends ADR-093 and ADR-094 (the shared card, the mark, the pieces that draw icons), ADR-087 (an icon is paid for by every route that loads it), ADR-089 (a status has a shape, an empty list says what to do) and ADR-095 (a repeated control is named for its row). Web only and frontend only: no migration, no API or contract change (54 operations), no new icon, no new message string.</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-087, ADR-089, ADR-093, ADR-094, ADR-095</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N96"/>
+  <autoFilter ref="A1:N97"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8394,8 +8466,30 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 87</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-096</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A State Is a Word With a Shape on a Card That Looks Like the Others, a Notice Has a Picture of Its Kind, and a Shared Section Takes Its Mark From the Page That Wants It</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D40"/>
+  <autoFilter ref="A1:D41"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 82 of 96 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-096.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 83 of 97 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-097.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 6079039 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 8b83944 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82</t>
+          <t xml:space="preserve">83</t>
         </is>
       </c>
     </row>
@@ -7335,8 +7335,80 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-097</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Workspace's Rows Say Where Things Stand With a Shape, a Dashboard Figure Has a Mark, and Neither Workspace Is in the Route's First Load</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- A vacancy's and a course's state is StatusChip from cards/listing-look: four states (removed, draft, live, closed), a tone and a shape each, decided by two small pure functions (jobState, courseState) so a takedown wins over a draft and a published-but-not-open vacancy is closed, never "published" (its page is still there, so "published" would call it open) and an is_open that is absent is not guessed open. The…</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 88 (Epic B19, BL-19.18). Extends ADR-096 (a state is a word, a shape and a tone, one table per list), ADR-083 (one primary action per row, every control 44 px), ADR-087 and ADR-089 (the icon factory is paid for by every route that loads it), ADR-073's lesson about a ceiling and ADR-065 (a placeholder is the same shape as what replaces it). Web only and frontend only: no migration, no API or contract change (54 operations), no new icon, no new message string.</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-065, ADR-073, ADR-083, ADR-087, ADR-089, ADR-096</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N97"/>
+  <autoFilter ref="A1:N98"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8488,8 +8560,30 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 88</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-097</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Workspace's Rows Say Where Things Stand With a Shape, a Dashboard Figure Has a Mark, and Neither Workspace Is in the Route's First Load</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D41"/>
+  <autoFilter ref="A1:D42"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 83 of 97 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-097.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 84 of 98 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-098.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 8b83944 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 4cc0152 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83</t>
+          <t xml:space="preserve">84</t>
         </is>
       </c>
     </row>
@@ -7407,8 +7407,80 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-098</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Back Office and the Static Pages Say Where Things Stand With a Shape, a Complaint's State Is One Table for Both Its Readers, and the Error Page Has No Picture</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- A complaint's state is one table, cards/grievance-look (GRIEVANCE_LOOK: open, acknowledged, resolved, dismissed, each a tone and a shape), read by the operator's queue and by the sender's own list. Before, each had its own tone map and the person's list had no shape at all. - The overview's six figures are MetricTiles (ADR-097), each with a mark and a dash while the number has not arrived, the same shape before…</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 89 (Epic B19, BL-19.19 and BL-19.20). Extends ADR-096 and ADR-097 (a state is a word, a shape and a tone, one table per list; a figure has a mark), ADR-083 (the back office's structure and the 44 px floor), ADR-089 (the barrel puts what it names on every route) and ADR-087 (an icon is paid for by every route that loads it). Web only and frontend only: no migration, no API or contract change (54 operations), no new icon, no new message string.</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-083, ADR-087, ADR-089, ADR-096, ADR-097</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N98"/>
+  <autoFilter ref="A1:N99"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8582,8 +8654,30 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 89</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-098</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Back Office and the Static Pages Say Where Things Stand With a Shape, a Complaint's State Is One Table for Both Its Readers, and the Error Page Has No Picture</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D42"/>
+  <autoFilter ref="A1:D43"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 84 of 98 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-098.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 85 of 99 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-099.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 4cc0152 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 032a0e6 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84</t>
+          <t xml:space="preserve">85</t>
         </is>
       </c>
     </row>
@@ -7479,8 +7479,80 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-099</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text That Does Not Fit Is Wrapped or Broken and Never Cut Off, a Page Is Checked at Twice the Size in Every Language, and the Review Says What It Could Not Run</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- body { overflow-wrap: anywhere } in globals.css. Not break-word: both break a word that would otherwise overflow, but anywhere also counts the break in the element's minimum width, so a flex item holding "documents/instructions/correspondence" can shrink instead of widening the page. It acts only on a word that would overflow, so ordinary text is unchanged (checked: page heights identical with the rule on and…</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 90 (Epic B19, BL-19.25 and BL-19.26). Extends ADR-086 (the type scale: secondary text is 15 px and the floor is 12 px), ADR-077 (accessibility is held by the properties that produce it, and by saying what a test cannot see) and ADR-065 (a page that works at one size is not a page that works). Web only and frontend only: no migration, no API or contract change (54 operations), no new icon, no new message string.</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-065, ADR-077, ADR-086</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N99"/>
+  <autoFilter ref="A1:N100"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8676,8 +8748,30 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 90</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-099</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text That Does Not Fit Is Wrapped or Broken and Never Cut Off, a Page Is Checked at Twice the Size in Every Language, and the Review Says What It Could Not Run</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D43"/>
+  <autoFilter ref="A1:D44"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 85 of 99 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-099.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 86 of 100 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-100.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 032a0e6 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit bd317c6 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85</t>
+          <t xml:space="preserve">86</t>
         </is>
       </c>
     </row>
@@ -7551,8 +7551,80 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-100</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Home Knows Who Is Signed In, a Group That Has Begun Is Not an Intake, a Reply Date Is an Ask, a Vacancy Starts From a Role, and the Colour Is Decided on the Product's Own Shapes Before It Is Changed</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- The home page's right-hand card is for a visitor or for a person, not for both (HomeAccess). A signed-in person sees "Welcome back" and their own doors (their matches if they look for work, up to three organisations, the most recently used first, the rest named as in the menu); the sign-up chooser is server-rendered and stays what a visitor and a browser without JavaScript get, and returns when /auth/me refuses…</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 91 (Epic B22, BL-22.1 to BL-22.3; Epic B21, BL-21.1). Extends ADR-080 (a signed-in home is the person's own), ADR-068 (a fact about a course that changes is derived, and a recommendation says whether you can act on it), ADR-063 (a job_role expands to compulsory standards, importance 3, mandatory off) and ADR-086 (the look is a token). Web only and frontend only: no migration, no API or contract change (54 operations), no new icon.</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-063, ADR-068, ADR-080, ADR-086</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N100"/>
+  <autoFilter ref="A1:N101"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8770,8 +8842,30 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 91</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-100</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Home Knows Who Is Signed In, a Group That Has Begun Is Not an Intake, a Reply Date Is an Ask, a Vacancy Starts From a Role, and the Colour Is Decided on the Product's Own Shapes Before It Is Changed</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D44"/>
+  <autoFilter ref="A1:D45"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 86 of 100 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-100.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 87 of 101 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-101.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit bd317c6 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit b02587d by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86</t>
+          <t xml:space="preserve">87</t>
         </is>
       </c>
     </row>
@@ -7623,8 +7623,80 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-101</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Brand Is Deep Teal, Success Is Moved to a True Green Because Hue Is Measured and Not Guessed, the Highlight Is Decoration Only, and the Public Sees a Score Only From Three Ratings</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Deep teal. Brand ramp #ecf8f8 to #062629, 700 is #0f5c63 (7.7:1 on white, 7.3 on the page, white on it 7.7), dark brand is 400 #35a5ac (6.3:1 on the dark page). The neutral greys are unchanged (the owner kept them), so the address bar's colours, the manifest's background, the offline page and the phone's splash did not move. The mapping of each semantic token to a ramp step is unchanged, which is why every…</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 92 (Epic B21, BL-21.2 to BL-21.5; Epic B22, BL-22.4 in part and BL-22.6). Supersedes the part of ADR-086 that fixed brand-700 at the product's old blue (#1f4e79, "the colour the product has always used"); everything else in ADR-086 stands (the look is a token, a ramp step is never a class, text is never translucent). Extends ADR-096 (a state is a word, a shape and a tone). Web and phone, frontend only: no migration, no API or contract change (54 operations), no new icon.</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-086, ADR-096</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N101"/>
+  <autoFilter ref="A1:N102"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8864,8 +8936,30 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 92</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-101</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Brand Is Deep Teal, Success Is Moved to a True Green Because Hue Is Measured and Not Guessed, the Highlight Is Decoration Only, and the Public Sees a Score Only From Three Ratings</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D45"/>
+  <autoFilter ref="A1:D46"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 86 of 100 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-100.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 87 of 101 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-101.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit bd317c6 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit b02587d by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86</t>
+          <t xml:space="preserve">87</t>
         </is>
       </c>
     </row>
@@ -7623,8 +7623,80 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-101</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Light Is the Default Because a Dark Computer Hid the Light Page, a Colour Is Judged on the Product Before It Is Chosen, and the Public Sees a Score Only From Three Ratings</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Light is the default, whatever the device says. A visitor who never touches the control gets the light page; dark and "match the device" are choices. lib/theme.ts: a stored value is a choice only if it is dark or system, anything else (or nothing, or storage that throws) is light; choosing light removes the stored value, because light is the absence of one. &lt;html data-theme&gt; is absent for light, dark for dark…</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted (October 2026). Sprint 92 (Epic B21, closed without a palette change; Epic B22, BL-22.4 in part, BL-22.6 and BL-22.10). Supersedes the part of ADR-087 that said the product follows the device's colour scheme until a person chooses; everything else in ADR-087 stands. Web and phone, frontend only: no migration, no API or contract change (54 operations), no new icon. The brand stays blue (#1f4e79, ADR-086).</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-086, ADR-087</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N101"/>
+  <autoFilter ref="A1:N102"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8864,8 +8936,30 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 92</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-101</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Light Is the Default Because a Dark Computer Hid the Light Page, a Colour Is Judged on the Product Before It Is Chosen, and the Public Sees a Score Only From Three Ratings</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D45"/>
+  <autoFilter ref="A1:D46"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 87 of 101 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-101.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 88 of 102 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-102.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit b02587d by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 25c4637 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87</t>
+          <t xml:space="preserve">88</t>
         </is>
       </c>
     </row>
@@ -7695,8 +7695,80 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-102</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Training Organisation Sells Courses, Delivers Training, or Both; a Centre Is a Child of the Organisation That Delivers; Delivery of Somebody Else's Course Needs Their Approval</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- One organisation, two capabilities. The public word is training organisation; it is stored as tenant_type = "course_provider" (unchanged: a rename strands listings, bulk-upload files and the released phone contract). It has up to two capabilities, stored as two booleans on the tenant, not as two types: publishes_courses ("course provider": publishes courses and receives course-level interest; default true,…</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted as a design (October 2026), to be built in Sprints 94 to 101. Written in Sprint 93 (Epic B18, BL-18.1; Epic B20 is built on it). Extends ADR-026 (a course provider publishes through its own writer), ADR-038 (one identity, many roles: never fork an account), ADR-039 (authorization asks for a permission), ADR-042 (operator authority is outside the tenant model), ADR-068 (a fact about a course that changes is derived) and ADR-069 (every writer of "published" has the one guard). Supersedes nothing. Nothing in this ADR is implemented yet, and Sprint 93 changes no behaviour of it: the sprint makes the room (first-load budget) and the operator's queue search that Sprints 94 to 101 need.</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-026, ADR-038, ADR-039, ADR-042, ADR-068, ADR-069</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N102"/>
+  <autoFilter ref="A1:N103"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -8958,8 +9030,30 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 93</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-102</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Training Organisation Sells Courses, Delivers Training, or Both; a Centre Is a Child of the Organisation That Delivers; Delivery of Somebody Else's Course Needs Their Approval</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D46"/>
+  <autoFilter ref="A1:D47"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 25c4637 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit d5a832d by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -7713,12 +7713,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93</t>
+          <t xml:space="preserve">94</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">0058</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted as a design (October 2026), to be built in Sprints 94 to 101. Written in Sprint 93 (Epic B18, BL-18.1; Epic B20 is built on it). Extends ADR-026 (a course provider publishes through its own writer), ADR-038 (one identity, many roles: never fork an account), ADR-039 (authorization asks for a permission), ADR-042 (operator authority is outside the tenant model), ADR-068 (a fact about a course that changes is derived) and ADR-069 (every writer of "published" has the one guard). Supersedes nothing. Nothing in this ADR is implemented yet, and Sprint 93 changes no behaviour of it: the sprint makes the room (first-load budget) and the operator's queue search that Sprints 94 to 101 need.</t>
+          <t xml:space="preserve">Accepted (October 2026); the capabilities, registration, profile and public page are built in Sprint 94 (migration 0058), the rest in Sprints 95 to 101. Written in Sprint 93 (Epic B18, BL-18.1; Epic B20 is built on it). Extends ADR-026 (a course provider publishes through its own writer), ADR-038 (one identity, many roles: never fork an account), ADR-039 (authorization asks for a permission), ADR-042 (operator authority is outside the tenant model), ADR-068 (a fact about a course that changes is derived) and ADR-069 (every writer of "published" has the one guard). Supersedes nothing. Sprint 93 changed no behaviour of it: the sprint made the room (first-load budget) and the operator's queue search that Sprints 94 to 101 need.</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -9033,7 +9033,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 93</t>
+          <t xml:space="preserve">Sprint 94</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">0058</t>
         </is>
       </c>
     </row>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit d5a832d by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 16f7484 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted (October 2026); the capabilities, registration, profile and public page are built in Sprint 94 (migration 0058), the rest in Sprints 95 to 101. Written in Sprint 93 (Epic B18, BL-18.1; Epic B20 is built on it). Extends ADR-026 (a course provider publishes through its own writer), ADR-038 (one identity, many roles: never fork an account), ADR-039 (authorization asks for a permission), ADR-042 (operator authority is outside the tenant model), ADR-068 (a fact about a course that changes is derived) and ADR-069 (every writer of "published" has the one guard). Supersedes nothing. Sprint 93 changed no behaviour of it: the sprint made the room (first-load budget) and the operator's queue search that Sprints 94 to 101 need.</t>
+          <t xml:space="preserve">Accepted (October 2026); the capabilities, registration, profile and public page are built in Sprint 94 (migration 0058), centres in Sprint 95 (migration 0059), the rest in Sprints 96 to 101. Written in Sprint 93 (Epic B18, BL-18.1; Epic B20 is built on it). Extends ADR-026 (a course provider publishes through its own writer), ADR-038 (one identity, many roles: never fork an account), ADR-039 (authorization asks for a permission), ADR-042 (operator authority is outside the tenant model), ADR-068 (a fact about a course that changes is derived) and ADR-069 (every writer of "published" has the one guard). Supersedes nothing. Sprint 93 changed no behaviour of it: the sprint made the room (first-load budget) and the operator's queue search that Sprints 94 to 101 need.</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 16f7484 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit d94145e by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted (October 2026); the capabilities, registration, profile and public page are built in Sprint 94 (migration 0058), centres in Sprint 95 (migration 0059), the rest in Sprints 96 to 101. Written in Sprint 93 (Epic B18, BL-18.1; Epic B20 is built on it). Extends ADR-026 (a course provider publishes through its own writer), ADR-038 (one identity, many roles: never fork an account), ADR-039 (authorization asks for a permission), ADR-042 (operator authority is outside the tenant model), ADR-068 (a fact about a course that changes is derived) and ADR-069 (every writer of "published" has the one guard). Supersedes nothing. Sprint 93 changed no behaviour of it: the sprint made the room (first-load budget) and the operator's queue search that Sprints 94 to 101 need.</t>
+          <t xml:space="preserve">Accepted (October 2026); the capabilities, registration, profile and public page are built in Sprint 94 (migration 0058), centres in Sprint 95 (migration 0059), centre staff in Sprint 96 (migration 0060), the rest in Sprints 97 to 101. Written in Sprint 93 (Epic B18, BL-18.1; Epic B20 is built on it). Extends ADR-026 (a course provider publishes through its own writer), ADR-038 (one identity, many roles: never fork an account), ADR-039 (authorization asks for a permission), ADR-042 (operator authority is outside the tenant model), ADR-068 (a fact about a course that changes is derived) and ADR-069 (every writer of "published" has the one guard). Supersedes nothing. Sprint 93 changed no behaviour of it: the sprint made the room (first-load budget) and the operator's queue search that Sprints 94 to 101 need.</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -153,7 +153,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 88 of 102 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-102.</t>
+          <t xml:space="preserve">Yes. It is the live decision record, not a historical artefact. 89 of 103 ADRs are in force or extended by a later one. It is append-only by design: later ADRs refine, extend or supersede earlier ones, and the file is kept up to date through ADR-103.</t>
         </is>
       </c>
     </row>
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit d94145e by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 09d3f43 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88</t>
+          <t xml:space="preserve">89</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted (October 2026); the capabilities, registration, profile and public page are built in Sprint 94 (migration 0058), centres in Sprint 95 (migration 0059), centre staff in Sprint 96 (migration 0060), the rest in Sprints 97 to 101. Written in Sprint 93 (Epic B18, BL-18.1; Epic B20 is built on it). Extends ADR-026 (a course provider publishes through its own writer), ADR-038 (one identity, many roles: never fork an account), ADR-039 (authorization asks for a permission), ADR-042 (operator authority is outside the tenant model), ADR-068 (a fact about a course that changes is derived) and ADR-069 (every writer of "published" has the one guard). Supersedes nothing. Sprint 93 changed no behaviour of it: the sprint made the room (first-load budget) and the operator's queue search that Sprints 94 to 101 need.</t>
+          <t xml:space="preserve">Accepted (October 2026); the capabilities, registration, profile and public page are built in Sprint 94 (migration 0058), centres in Sprint 95 (migration 0059), centre staff in Sprint 96 (migration 0060), delivery authorisations in Sprint 97 (migration 0061), the rest in Sprints 98 to 101. Written in Sprint 93 (Epic B18, BL-18.1; Epic B20 is built on it). Extends ADR-026 (a course provider publishes through its own writer), ADR-038 (one identity, many roles: never fork an account), ADR-039 (authorization asks for a permission), ADR-042 (operator authority is outside the tenant model), ADR-068 (a fact about a course that changes is derived) and ADR-069 (every writer of "published" has the one guard). Supersedes nothing. Sprint 93 changed no behaviour of it: the sprint made the room (first-load budget) and the operator's queue search that Sprints 94 to 101 need.</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -7767,8 +7767,80 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-103</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Batch Is a Course Run at a Centre, a Seat Is Derived, a Revocation Reaches Open Batches Through a Hook, and a Learner's Contact Reaches Only Who Runs the Class</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2026</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0061</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active – extends earlier ADR</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- A batch is one run of one course at one centre: batches(id, course_id, centre_id, starts_on, ends_on?, seats?, fee_inr?, status, created_at, …). The delivering organisation is the centre's parent, derived and never stored on the batch. Stored status is only draft, published or cancelled; open, full, running and finished are derived from the dates and the seats at read time (ADR-068: a stored flag is wrong the…</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposed (October 2026), written in Sprint 97 (Epic B18, BL-18.5; Epic B20 is built on it). The delivery authorisations it depends on are built (ADR-102, migration 0061); the batch itself is Sprint 98. Three decisions are the owner's and are written here as recommendations, marked below; nothing in Sprint 98 is built on them until the owner confirms or changes them. Extends ADR-102 (centres, authorisations), ADR-068 (a fact about a course that changes is derived), ADR-071 (a join table, never a foreign key into a module that may not be imported), ADR-082 (require_not_paused guards every writer of contact) and ADR-025/047 (the enrolment metric).</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-025, ADR-068, ADR-071, ADR-082, ADR-102</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR header and sprint record in CLAUDE.md / projectContextForMe.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N103"/>
+  <autoFilter ref="A1:N104"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -9052,8 +9124,30 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint 97</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-103</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Batch Is a Course Run at a Centre, a Seat Is Derived, a Revocation Reaches Open Batches Through a Hook, and a Learner's Contact Reaches Only Who Runs the Class</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0061</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D47"/>
+  <autoFilter ref="A1:D48"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 09d3f43 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 8b89bb5 by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">October 2026</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97</t>
+          <t xml:space="preserve">98</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposed (October 2026), written in Sprint 97 (Epic B18, BL-18.5; Epic B20 is built on it). The delivery authorisations it depends on are built (ADR-102, migration 0061); the batch itself is Sprint 98. Three decisions are the owner's and are written here as recommendations, marked below; nothing in Sprint 98 is built on them until the owner confirms or changes them. Extends ADR-102 (centres, authorisations), ADR-068 (a fact about a course that changes is derived), ADR-071 (a join table, never a foreign key into a module that may not be imported), ADR-082 (require_not_paused guards every writer of contact) and ADR-025/047 (the enrolment metric).</t>
+          <t xml:space="preserve">Proposed (October 2026; the batch itself built in Sprint 98, see the end), written in Sprint 97 (Epic B18, BL-18.5; Epic B20 is built on it). The delivery authorisations it depends on are built (ADR-102, migration 0061); the batch itself is Sprint 98. Three decisions are the owner's and are written here as recommendations, marked below; nothing in Sprint 98 is built on them until the owner confirms or changes them. Extends ADR-102 (centres, authorisations), ADR-068 (a fact about a course that changes is derived), ADR-071 (a join table, never a foreign key into a module that may not be imported), ADR-082 (require_not_paused guards every writer of contact) and ADR-025/047 (the enrolment metric).</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sprint 97</t>
+          <t xml:space="preserve">Sprint 98</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 8b89bb5 by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit d8f881f by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>

--- a/docs/adr/IISM-ADR-Register.xlsx
+++ b/docs/adr/IISM-ADR-Register.xlsx
@@ -225,7 +225,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit d8f881f by scripts/build_adr_register.py.</t>
+          <t xml:space="preserve">From docs/adr/architecture-decisions.md at commit 11d226c by scripts/build_adr_register.py.</t>
         </is>
       </c>
     </row>
